--- a/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -42542,11 +42542,32 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37&amp;38</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1235呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 594呎 (2房)
 $1678万
@@ -42554,7 +42575,7 @@
 (24年-05月-27日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 749呎 (3房)
 $2413万
@@ -42562,8 +42583,8 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
 $1726万
@@ -42571,7 +42592,7 @@
 (24年-06月-12日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 343呎 (1房)
 $1216万
@@ -42579,7 +42600,7 @@
 (21年-09月-20日)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 470呎 (2房)
 $1707万
@@ -42587,27 +42608,6 @@
 (22年-05月-27日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37&amp;38</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>A | 1235呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -42542,10 +42542,59 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 594呎 (2房)
+$1678万
+$28,251/呎
+(24年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+$2413万
+$32,213/呎
+(24年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1726万
+$31,211/呎
+(24年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 343呎 (1房)
+$1216万
+$35,464/呎
+(21年-09月-20日)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 470呎 (2房)
+$1707万
+$36,317/呎
+(22年-05月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37&amp;38</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 1235呎 (3房)
 -
@@ -42553,61 +42602,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 594呎 (2房)
-$1678万
-$28,251/呎
-(24年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-$2413万
-$32,213/呎
-(24年-04月-26日)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1726万
-$31,211/呎
-(24年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>F | 343呎 (1房)
-$1216万
-$35,464/呎
-(21年-09月-20日)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>G | 470呎 (2房)
-$1707万
-$36,317/呎
-(22年-05月-27日)</t>
-        </is>
-      </c>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -32894,11 +32894,32 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37&amp;38</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1235呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 594呎 (2房)
 $1678万
@@ -32906,7 +32927,7 @@
 (24年-05月-26日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 749呎 (3房)
 $2413万
@@ -32914,8 +32935,8 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
 $1726万
@@ -32923,7 +32944,7 @@
 (24年-06月-11日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 343呎 (1房)
 $1216万
@@ -32931,7 +32952,7 @@
 (21年-09月-19日)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 470呎 (2房)
 $1707万
@@ -32939,27 +32960,6 @@
 (22年-05月-26日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37&amp;38</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>A | 1235呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -32894,10 +32894,59 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 594呎 (2房)
+$1678万
+$28,251/呎
+(24年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+$2413万
+$32,213/呎
+(24年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1726万
+$31,211/呎
+(24年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 343呎 (1房)
+$1216万
+$35,464/呎
+(21年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 470呎 (2房)
+$1707万
+$36,317/呎
+(22年-05月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37&amp;38</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 1235呎 (3房)
 -
@@ -32905,61 +32954,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 594呎 (2房)
-$1678万
-$28,251/呎
-(24年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-$2413万
-$32,213/呎
-(24年-04月-25日)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1726万
-$31,211/呎
-(24年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>F | 343呎 (1房)
-$1216万
-$35,464/呎
-(21年-09月-19日)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>G | 470呎 (2房)
-$1707万
-$36,317/呎
-(22年-05月-26日)</t>
-        </is>
-      </c>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
